--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488272_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488272_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.8379</v>
+        <v>8.376799999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>5.9122</v>
+        <v>6.4019</v>
       </c>
       <c r="F2" t="n">
-        <v>1.9257</v>
+        <v>1.975</v>
       </c>
       <c r="G2" t="n">
         <v>4.2501</v>
@@ -610,13 +610,13 @@
         <v>1.8529</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.4683</v>
+        <v>0.0706</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.7996</v>
+        <v>-0.3099</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3313</v>
+        <v>0.3805</v>
       </c>
       <c r="V2" t="n">
         <v>2.2033</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.1891</v>
+        <v>5.8455</v>
       </c>
       <c r="E3" t="n">
-        <v>5.2195</v>
+        <v>5.0237</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9696</v>
+        <v>0.8218</v>
       </c>
       <c r="G3" t="n">
         <v>3.2416</v>
@@ -688,13 +688,13 @@
         <v>1.8529</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1328</v>
+        <v>-0.2108</v>
       </c>
       <c r="T3" t="n">
-        <v>0.051</v>
+        <v>-0.1449</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0818</v>
+        <v>-0.0659</v>
       </c>
       <c r="V3" t="n">
         <v>1.8883</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. DIAZ FERREIRA</t>
+          <t>A. MENDEZ CARRION</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.3851</v>
+        <v>5.7082</v>
       </c>
       <c r="E4" t="n">
-        <v>3.2455</v>
+        <v>3.9759</v>
       </c>
       <c r="F4" t="n">
-        <v>2.1396</v>
+        <v>1.7323</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3071</v>
+        <v>3.7824</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2809</v>
+        <v>3.013</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0263</v>
+        <v>0.7695</v>
       </c>
       <c r="J4" t="n">
-        <v>0.167</v>
+        <v>3.811</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.0819</v>
+        <v>3.1261</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2488</v>
+        <v>0.6849</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1402</v>
+        <v>-0.0285</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3627</v>
+        <v>-0.1131</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.2226</v>
+        <v>0.08459999999999999</v>
       </c>
       <c r="P4" t="n">
-        <v>1.6676</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R4" t="n">
-        <v>1.6676</v>
+        <v>1.4823</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8921</v>
+        <v>0.1116</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5609</v>
+        <v>-0.1669</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3313</v>
+        <v>0.2785</v>
       </c>
       <c r="V4" t="n">
-        <v>2.5183</v>
+        <v>1.2583</v>
       </c>
       <c r="W4" t="n">
-        <v>2.5177</v>
+        <v>1.2583</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0005</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>5.2824</v>
+        <v>5.2085</v>
       </c>
       <c r="E5" t="n">
         <v>2.7413</v>
       </c>
       <c r="F5" t="n">
-        <v>2.5411</v>
+        <v>2.4672</v>
       </c>
       <c r="G5" t="n">
         <v>3.8711</v>
@@ -844,13 +844,13 @@
         <v>2.2234</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1149</v>
+        <v>0.041</v>
       </c>
       <c r="T5" t="n">
         <v>-0.2773</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3922</v>
+        <v>0.3183</v>
       </c>
       <c r="V5" t="n">
         <v>-0.0005</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. MENDEZ CARRION</t>
+          <t>A. DIAZ FERREIRA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>5.1447</v>
+        <v>4.9447</v>
       </c>
       <c r="E6" t="n">
-        <v>3.4863</v>
+        <v>2.7559</v>
       </c>
       <c r="F6" t="n">
-        <v>1.6584</v>
+        <v>2.1888</v>
       </c>
       <c r="G6" t="n">
-        <v>3.7824</v>
+        <v>0.3071</v>
       </c>
       <c r="H6" t="n">
-        <v>3.013</v>
+        <v>0.2809</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7695</v>
+        <v>0.0263</v>
       </c>
       <c r="J6" t="n">
-        <v>3.811</v>
+        <v>0.167</v>
       </c>
       <c r="K6" t="n">
-        <v>3.1261</v>
+        <v>-0.0819</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6849</v>
+        <v>0.2488</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.0285</v>
+        <v>0.1402</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1131</v>
+        <v>0.3627</v>
       </c>
       <c r="O6" t="n">
-        <v>0.08459999999999999</v>
+        <v>-0.2226</v>
       </c>
       <c r="P6" t="n">
-        <v>0.5558999999999999</v>
+        <v>1.6676</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.4823</v>
+        <v>1.6676</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4519</v>
+        <v>0.4517</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6566</v>
+        <v>0.0712</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2047</v>
+        <v>0.3805</v>
       </c>
       <c r="V6" t="n">
-        <v>1.2583</v>
+        <v>2.5183</v>
       </c>
       <c r="W6" t="n">
-        <v>1.2583</v>
+        <v>2.5177</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>0.0005</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>4.0195</v>
+        <v>3.8975</v>
       </c>
       <c r="E7" t="n">
-        <v>3.8962</v>
+        <v>3.7004</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1233</v>
+        <v>0.1972</v>
       </c>
       <c r="G7" t="n">
         <v>3.1371</v>
@@ -1000,13 +1000,13 @@
         <v>2.0382</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2119</v>
+        <v>-0.3339</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0373</v>
+        <v>-0.2331</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1746</v>
+        <v>-0.1007</v>
       </c>
       <c r="V7" t="n">
         <v>-0.9439</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. IDRIS IGENE</t>
+          <t>J. NIELSEN HIDALGO MARTIN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.8994</v>
+        <v>2.2156</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3774</v>
+        <v>1.9453</v>
       </c>
       <c r="F8" t="n">
-        <v>2.522</v>
+        <v>0.2703</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2723</v>
+        <v>-0.663</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8988</v>
+        <v>-0.018</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.6266</v>
+        <v>-0.6451</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1321</v>
+        <v>0.7168</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5361</v>
+        <v>-0.0819</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.404</v>
+        <v>0.7986</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1402</v>
+        <v>-1.3798</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3627</v>
+        <v>0.0639</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.2226</v>
+        <v>-1.4437</v>
       </c>
       <c r="P8" t="n">
-        <v>1.6676</v>
+        <v>0.9264</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R8" t="n">
-        <v>1.6676</v>
+        <v>1.8529</v>
       </c>
       <c r="S8" t="n">
-        <v>1.2751</v>
+        <v>-0.5655</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5609</v>
+        <v>-0.3628</v>
       </c>
       <c r="U8" t="n">
-        <v>0.7143</v>
+        <v>-0.2027</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.3155</v>
+        <v>2.5177</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.3155</v>
+        <v>2.5177</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P. OSÉS BERNALDÉZ</t>
+          <t>S. IDRIS IGENE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>2.2103</v>
+        <v>2.2128</v>
       </c>
       <c r="E9" t="n">
-        <v>2.2103</v>
+        <v>-0.1122</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>2.325</v>
       </c>
       <c r="G9" t="n">
-        <v>2.2103</v>
+        <v>0.2723</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9661999999999999</v>
+        <v>0.8988</v>
       </c>
       <c r="I9" t="n">
-        <v>1.2441</v>
+        <v>-0.6266</v>
       </c>
       <c r="J9" t="n">
-        <v>2.2103</v>
+        <v>0.1321</v>
       </c>
       <c r="K9" t="n">
-        <v>0.9661999999999999</v>
+        <v>0.5361</v>
       </c>
       <c r="L9" t="n">
-        <v>1.2441</v>
+        <v>-0.404</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>0.1402</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>0.3627</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>-0.2226</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.6676</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.6676</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>0.5885</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>0.0712</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>0.5173</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-0.3155</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>-0.3155</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. NIELSEN HIDALGO MARTIN</t>
+          <t>P. OSÉS BERNALDÉZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>1.8233</v>
+        <v>2.2103</v>
       </c>
       <c r="E10" t="n">
-        <v>1.6515</v>
+        <v>2.2103</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1718</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.663</v>
+        <v>2.2103</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.018</v>
+        <v>0.9661999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.6451</v>
+        <v>1.2441</v>
       </c>
       <c r="J10" t="n">
-        <v>0.7168</v>
+        <v>2.2103</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.0819</v>
+        <v>0.9661999999999999</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7986</v>
+        <v>1.2441</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.3798</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0639</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.4437</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>0.9264</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.8529</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.9578</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6566</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3012</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>2.5177</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>2.5177</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9298</v>
+        <v>1.2729</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0354</v>
+        <v>0.3292</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8944</v>
+        <v>0.9437</v>
       </c>
       <c r="G11" t="n">
         <v>0.0887</v>
@@ -1312,13 +1312,13 @@
         <v>1.1117</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2706</v>
+        <v>0.07240000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1977</v>
+        <v>0.0961</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.07290000000000001</v>
+        <v>-0.0236</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. RODRIGUEZ LEIRO</t>
+          <t>J. NIELSEN HIDALGO MARTÍN</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3758</v>
+        <v>0.3221</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.7178</v>
+        <v>0.3221</v>
       </c>
       <c r="F12" t="n">
-        <v>1.0936</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.1955</v>
+        <v>0.3221</v>
       </c>
       <c r="H12" t="n">
-        <v>0.6262</v>
+        <v>0.3221</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.8216</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0.7696</v>
+        <v>0.3221</v>
       </c>
       <c r="K12" t="n">
-        <v>0.5623</v>
+        <v>0.3221</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2074</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.9651</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>0.0639</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.029</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.8529</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.8529</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0587</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>0.051</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1097</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>0.63</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>0.3144</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0.3155</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. NIELSEN HIDALGO MARTÍN</t>
+          <t>A. RODRIGUEZ LEIRO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3221</v>
+        <v>0.1553</v>
       </c>
       <c r="E13" t="n">
-        <v>0.3221</v>
+        <v>-0.9137</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>1.069</v>
       </c>
       <c r="G13" t="n">
-        <v>0.3221</v>
+        <v>-0.1955</v>
       </c>
       <c r="H13" t="n">
-        <v>0.3221</v>
+        <v>0.6262</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>-0.8216</v>
       </c>
       <c r="J13" t="n">
-        <v>0.3221</v>
+        <v>0.7696</v>
       </c>
       <c r="K13" t="n">
-        <v>0.3221</v>
+        <v>0.5623</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>0.2074</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>-0.9651</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>0.0639</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>-1.029</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-1.8529</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.8529</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>-0.2792</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>-0.1449</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>-0.1343</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.63</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>0.3144</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>0.3155</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.1525</v>
+        <v>-0.1033</v>
       </c>
       <c r="E14" t="n">
         <v>1.3112</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.4637</v>
+        <v>-1.4145</v>
       </c>
       <c r="G14" t="n">
         <v>1.6285</v>
@@ -1546,13 +1546,13 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.2072</v>
+        <v>-0.1579</v>
       </c>
       <c r="T14" t="n">
         <v>-0.1094</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0977</v>
+        <v>-0.0485</v>
       </c>
       <c r="V14" t="n">
         <v>-1.5738</v>
@@ -1582,7 +1582,7 @@
         <v>42.2669</v>
       </c>
       <c r="E15" t="n">
-        <v>29.6911</v>
+        <v>29.6913</v>
       </c>
       <c r="F15" t="n">
         <v>12.5758</v>
@@ -1624,13 +1624,13 @@
         <v>17.6024</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2115</v>
+        <v>-0.2114999999999999</v>
       </c>
       <c r="T15" t="n">
         <v>-1.5107</v>
       </c>
       <c r="U15" t="n">
-        <v>1.2995</v>
+        <v>1.2994</v>
       </c>
       <c r="V15" t="n">
         <v>8.1822</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. RODRIGUEZ TORRERO</t>
+          <t>Á. GONZÁLEZ PALOMO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6432</v>
+        <v>0.3221</v>
       </c>
       <c r="E16" t="n">
-        <v>1.3588</v>
+        <v>0.3221</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.7157</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.9367</v>
+        <v>0.3221</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.9123</v>
+        <v>0.3221</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.0245</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6242</v>
+        <v>0.3221</v>
       </c>
       <c r="K16" t="n">
-        <v>0.4891</v>
+        <v>0.3221</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1351</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.561</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.4014</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.1596</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.1117</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1117</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>2.0976</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>1.0496</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.048</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.6294</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.315</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.3144</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Á. GONZÁLEZ PALOMO</t>
+          <t>A. GONZALEZ PALOMO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3221</v>
+        <v>0.1091</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3221</v>
+        <v>3.2977</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>-3.1885</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3221</v>
+        <v>2.1216</v>
       </c>
       <c r="H17" t="n">
-        <v>0.3221</v>
+        <v>0.8746</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>1.247</v>
       </c>
       <c r="J17" t="n">
-        <v>0.3221</v>
+        <v>5.2973</v>
       </c>
       <c r="K17" t="n">
-        <v>0.3221</v>
+        <v>2.0612</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>3.236</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>-3.1757</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>-1.1867</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>-1.989</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.8529</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>0.9264</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>0.1729</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>-0.1467</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>0.3196</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-1.2589</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. GONZALEZ PALOMO</t>
+          <t>A. RODRIGUEZ TORRERO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0107</v>
+        <v>-0.7552</v>
       </c>
       <c r="E18" t="n">
-        <v>3.2977</v>
+        <v>0.4775</v>
       </c>
       <c r="F18" t="n">
-        <v>-3.287</v>
+        <v>-1.2327</v>
       </c>
       <c r="G18" t="n">
-        <v>2.1216</v>
+        <v>-1.9367</v>
       </c>
       <c r="H18" t="n">
-        <v>0.8746</v>
+        <v>-0.9123</v>
       </c>
       <c r="I18" t="n">
-        <v>1.247</v>
+        <v>-1.0245</v>
       </c>
       <c r="J18" t="n">
-        <v>5.2973</v>
+        <v>0.6242</v>
       </c>
       <c r="K18" t="n">
-        <v>2.0612</v>
+        <v>0.4891</v>
       </c>
       <c r="L18" t="n">
-        <v>3.236</v>
+        <v>0.1351</v>
       </c>
       <c r="M18" t="n">
-        <v>-3.1757</v>
+        <v>-2.561</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.1867</v>
+        <v>-1.4014</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.989</v>
+        <v>-1.1596</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.9264</v>
+        <v>1.1117</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.8529</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9264</v>
+        <v>1.1117</v>
       </c>
       <c r="S18" t="n">
-        <v>0.07439999999999999</v>
+        <v>0.6992</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1467</v>
+        <v>0.1682</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2211</v>
+        <v>0.531</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.2589</v>
+        <v>-0.6294</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>-0.315</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.2589</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.3094</v>
+        <v>-0.9903999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.196</v>
+        <v>-0.0002</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.1133</v>
+        <v>-0.9902</v>
       </c>
       <c r="G19" t="n">
         <v>-1.1726</v>
@@ -1936,13 +1936,13 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1368</v>
+        <v>0.1822</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2189</v>
+        <v>-0.023</v>
       </c>
       <c r="U19" t="n">
-        <v>0.08210000000000001</v>
+        <v>0.2052</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.3836</v>
+        <v>-3.253</v>
       </c>
       <c r="E21" t="n">
         <v>-1.9253</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.4583</v>
+        <v>-1.3277</v>
       </c>
       <c r="G21" t="n">
         <v>-1.8503</v>
@@ -2092,13 +2092,13 @@
         <v>0.9264</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5894</v>
+        <v>-0.4589</v>
       </c>
       <c r="T21" t="n">
         <v>-0.3656</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2239</v>
+        <v>-0.09329999999999999</v>
       </c>
       <c r="V21" t="n">
         <v>-0.9439</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.8884</v>
+        <v>-3.4715</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.7117</v>
+        <v>-2.4179</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.1767</v>
+        <v>-1.0535</v>
       </c>
       <c r="G22" t="n">
         <v>-1.5411</v>
@@ -2170,13 +2170,13 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4949</v>
+        <v>-0.078</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3283</v>
+        <v>-0.0345</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1666</v>
+        <v>-0.0435</v>
       </c>
       <c r="V22" t="n">
         <v>0.0005</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.4477</v>
+        <v>-4.3011</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.2025</v>
+        <v>-2.0066</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.2452</v>
+        <v>-2.2945</v>
       </c>
       <c r="G23" t="n">
         <v>-1.819</v>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>0.186</v>
+        <v>0.3326</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0547</v>
+        <v>0.1411</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2407</v>
+        <v>0.1915</v>
       </c>
       <c r="V23" t="n">
         <v>-1.8883</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>P. GOMEZ MORENO</t>
+          <t>A. ALVAREZ RICO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.1179</v>
+        <v>-4.973</v>
       </c>
       <c r="E24" t="n">
-        <v>1.1456</v>
+        <v>-2.054</v>
       </c>
       <c r="F24" t="n">
-        <v>-6.2636</v>
+        <v>-2.9189</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.6162</v>
+        <v>-3.6816</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.3798</v>
+        <v>-0.5298</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.2363</v>
+        <v>-3.1518</v>
       </c>
       <c r="J24" t="n">
-        <v>0.2874</v>
+        <v>-0.0448</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.1641</v>
+        <v>0.4422</v>
       </c>
       <c r="L24" t="n">
-        <v>1.4515</v>
+        <v>-0.487</v>
       </c>
       <c r="M24" t="n">
-        <v>-3.9035</v>
+        <v>-3.6368</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.2157</v>
+        <v>-0.972</v>
       </c>
       <c r="O24" t="n">
-        <v>-2.6878</v>
+        <v>-2.6648</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.7411</v>
+        <v>-1.6676</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.9264</v>
+        <v>-1.8529</v>
       </c>
       <c r="R24" t="n">
         <v>0.1853</v>
       </c>
       <c r="S24" t="n">
-        <v>0.1838</v>
+        <v>0.0612</v>
       </c>
       <c r="T24" t="n">
-        <v>0.2114</v>
+        <v>-0.1564</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0276</v>
+        <v>0.2176</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.9444</v>
+        <v>0.315</v>
       </c>
       <c r="W24" t="n">
-        <v>1.5733</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-2.5177</v>
+        <v>0.315</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A. ALVAREZ RICO</t>
+          <t>P. GOMEZ MORENO</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,73 +2359,73 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.1287</v>
+        <v>-5.3785</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.9561</v>
+        <v>0.656</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.1726</v>
+        <v>-6.0345</v>
       </c>
       <c r="G25" t="n">
-        <v>-3.6816</v>
+        <v>-3.6162</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.5298</v>
+        <v>-2.3798</v>
       </c>
       <c r="I25" t="n">
-        <v>-3.1518</v>
+        <v>-1.2363</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.0448</v>
+        <v>0.2874</v>
       </c>
       <c r="K25" t="n">
-        <v>0.4422</v>
+        <v>-1.1641</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.487</v>
+        <v>1.4515</v>
       </c>
       <c r="M25" t="n">
-        <v>-3.6368</v>
+        <v>-3.9035</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.972</v>
+        <v>-1.2157</v>
       </c>
       <c r="O25" t="n">
-        <v>-2.6648</v>
+        <v>-2.6878</v>
       </c>
       <c r="P25" t="n">
-        <v>-1.6676</v>
+        <v>-0.7411</v>
       </c>
       <c r="Q25" t="n">
-        <v>-1.8529</v>
+        <v>-0.9264</v>
       </c>
       <c r="R25" t="n">
         <v>0.1853</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.0945</v>
+        <v>-0.07679999999999999</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.0584</v>
+        <v>-0.2782</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.0361</v>
+        <v>0.2014</v>
       </c>
       <c r="V25" t="n">
-        <v>0.315</v>
+        <v>-0.9444</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.5733</v>
       </c>
       <c r="X25" t="n">
-        <v>0.315</v>
+        <v>-2.5177</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>R. FREIRE DELTIO</t>
+          <t>H. ANDRADE CORREIA E SILVA</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,73 +2437,73 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-8.725300000000001</v>
+        <v>-8.342000000000001</v>
       </c>
       <c r="E26" t="n">
-        <v>-5.6138</v>
+        <v>-3.8234</v>
       </c>
       <c r="F26" t="n">
-        <v>-3.1115</v>
+        <v>-4.5186</v>
       </c>
       <c r="G26" t="n">
-        <v>-4.3071</v>
+        <v>-1.2914</v>
       </c>
       <c r="H26" t="n">
-        <v>-2.9201</v>
+        <v>-2.4617</v>
       </c>
       <c r="I26" t="n">
-        <v>-1.387</v>
+        <v>1.1702</v>
       </c>
       <c r="J26" t="n">
-        <v>-1.6855</v>
+        <v>1.1532</v>
       </c>
       <c r="K26" t="n">
-        <v>-1.8727</v>
+        <v>-1.4607</v>
       </c>
       <c r="L26" t="n">
-        <v>0.1872</v>
+        <v>2.6139</v>
       </c>
       <c r="M26" t="n">
-        <v>-2.6217</v>
+        <v>-2.4447</v>
       </c>
       <c r="N26" t="n">
-        <v>-1.0474</v>
+        <v>-1.001</v>
       </c>
       <c r="O26" t="n">
-        <v>-1.5743</v>
+        <v>-1.4437</v>
       </c>
       <c r="P26" t="n">
         <v>-3.5205</v>
       </c>
       <c r="Q26" t="n">
-        <v>-3.7057</v>
+        <v>-4.6322</v>
       </c>
       <c r="R26" t="n">
-        <v>0.1853</v>
+        <v>1.1117</v>
       </c>
       <c r="S26" t="n">
-        <v>0.3611</v>
+        <v>-0.383</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.2226</v>
+        <v>-0.3444</v>
       </c>
       <c r="U26" t="n">
-        <v>0.5837</v>
+        <v>-0.0386</v>
       </c>
       <c r="V26" t="n">
-        <v>-1.2589</v>
+        <v>-3.1471</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>-1.2589</v>
+        <v>-3.1471</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>H. ANDRADE CORREIA E SILVA</t>
+          <t>R. FREIRE DELTIO</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2515,67 +2515,67 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-9.452999999999999</v>
+        <v>-8.791700000000001</v>
       </c>
       <c r="E27" t="n">
-        <v>-4.6068</v>
+        <v>-5.6138</v>
       </c>
       <c r="F27" t="n">
-        <v>-4.8462</v>
+        <v>-3.1779</v>
       </c>
       <c r="G27" t="n">
-        <v>-1.2914</v>
+        <v>-4.3071</v>
       </c>
       <c r="H27" t="n">
-        <v>-2.4617</v>
+        <v>-2.9201</v>
       </c>
       <c r="I27" t="n">
-        <v>1.1702</v>
+        <v>-1.387</v>
       </c>
       <c r="J27" t="n">
-        <v>1.1532</v>
+        <v>-1.6855</v>
       </c>
       <c r="K27" t="n">
-        <v>-1.4607</v>
+        <v>-1.8727</v>
       </c>
       <c r="L27" t="n">
-        <v>2.6139</v>
+        <v>0.1872</v>
       </c>
       <c r="M27" t="n">
-        <v>-2.4447</v>
+        <v>-2.6217</v>
       </c>
       <c r="N27" t="n">
-        <v>-1.001</v>
+        <v>-1.0474</v>
       </c>
       <c r="O27" t="n">
-        <v>-1.4437</v>
+        <v>-1.5743</v>
       </c>
       <c r="P27" t="n">
         <v>-3.5205</v>
       </c>
       <c r="Q27" t="n">
-        <v>-4.6322</v>
+        <v>-3.7057</v>
       </c>
       <c r="R27" t="n">
-        <v>1.1117</v>
+        <v>0.1853</v>
       </c>
       <c r="S27" t="n">
-        <v>-1.494</v>
+        <v>0.2947</v>
       </c>
       <c r="T27" t="n">
-        <v>-1.1279</v>
+        <v>-0.2226</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.3661</v>
+        <v>0.5173</v>
       </c>
       <c r="V27" t="n">
-        <v>-3.1471</v>
+        <v>-1.2589</v>
       </c>
       <c r="W27" t="n">
         <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>-3.1471</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="28">
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-42.26690000000001</v>
+        <v>-41.61409999999999</v>
       </c>
       <c r="E28" t="n">
-        <v>-12.5758</v>
+        <v>-12.5757</v>
       </c>
       <c r="F28" t="n">
-        <v>-29.6912</v>
+        <v>-29.0381</v>
       </c>
       <c r="G28" t="n">
         <v>-22.2526</v>
@@ -2638,13 +2638,13 @@
         <v>5.5585</v>
       </c>
       <c r="S28" t="n">
-        <v>0.2113999999999996</v>
+        <v>0.8641999999999999</v>
       </c>
       <c r="T28" t="n">
         <v>-1.2994</v>
       </c>
       <c r="U28" t="n">
-        <v>1.5107</v>
+        <v>2.1636</v>
       </c>
       <c r="V28" t="n">
         <v>-8.1821</v>
